--- a/Команды распознание.xlsx
+++ b/Команды распознание.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Toxa\Desktop\VK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF0D0FA2-5A98-4D4A-8C7A-E036F76937D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F80678E-86B3-44CB-BDD3-1A6A9F3D9CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3330" yWindow="0" windowWidth="18860" windowHeight="13460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Команды Жабабота" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
   <si>
     <t>Команды Жабабота</t>
   </si>
@@ -788,7 +788,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -802,6 +802,9 @@
     <row r="5" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">

--- a/Команды распознание.xlsx
+++ b/Команды распознание.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Toxa\Desktop\VK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F80678E-86B3-44CB-BDD3-1A6A9F3D9CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF0DF2D-70E2-4241-B6CD-16078649436B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6740" yWindow="340" windowWidth="18860" windowHeight="13460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Команды Жабабота" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="101">
   <si>
     <t>Команды Жабабота</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>В процессе</t>
+  </si>
+  <si>
+    <t>Нет</t>
   </si>
 </sst>
 </file>
@@ -804,38 +807,56 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="7" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="8" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="B8" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="9" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>67</v>
       </c>
+      <c r="B9" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="10" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="B10" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="11" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="B11" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="12" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
@@ -846,425 +867,647 @@
       <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="B13" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="14" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="B14" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="15" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>57</v>
       </c>
+      <c r="B15" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="16" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B35" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B36" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="49" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B49" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="52" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B51" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="53" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="54" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B53" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="55" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B54" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="57" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B56" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="58" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B57" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="59" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B58" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="60" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B59" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="61" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B60" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="62" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B61" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="64" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B63" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B64" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B65" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B66" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B67" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B68" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B75" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B76" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="78" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="79" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B78" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="80" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B80" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B81" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B82" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="6" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B83" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B84" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B85" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="87" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="88" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B87" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B88" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="90" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B89" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="91" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B90" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="92" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B91" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="93" spans="1:1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B92" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="94" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="95" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B94" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="96" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B95" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B96" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>56</v>
+      </c>
+      <c r="B97" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/Команды распознание.xlsx
+++ b/Команды распознание.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Toxa\Desktop\VK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF0DF2D-70E2-4241-B6CD-16078649436B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F81F14-510A-4A6F-971B-459A7C24A480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6740" yWindow="340" windowWidth="18860" windowHeight="13460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Команды Жабабота" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Команды Жабабота'!$A$1:$A$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Команды Жабабота'!$A$1:$B$97</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="102">
   <si>
     <t>Команды Жабабота</t>
   </si>
@@ -333,10 +333,13 @@
     <t>Да</t>
   </si>
   <si>
-    <t>В процессе</t>
-  </si>
-  <si>
     <t>Нет</t>
+  </si>
+  <si>
+    <t>Рандомные семена и прочее</t>
+  </si>
+  <si>
+    <t>+</t>
   </si>
 </sst>
 </file>
@@ -356,17 +359,23 @@
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1B1B1B"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
@@ -766,27 +775,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="80" customWidth="1"/>
     <col min="2" max="2" width="15.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="35" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -794,7 +806,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -802,7 +814,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -810,89 +822,95 @@
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="C7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="C8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -900,7 +918,7 @@
         <v>59</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -908,7 +926,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -916,7 +934,7 @@
         <v>61</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -924,7 +942,7 @@
         <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -932,7 +950,7 @@
         <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -945,7 +963,7 @@
         <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -953,7 +971,7 @@
         <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -966,7 +984,7 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -974,7 +992,7 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -982,7 +1000,7 @@
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
@@ -1000,7 +1018,7 @@
         <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1008,7 +1026,7 @@
         <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1016,7 +1034,7 @@
         <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1024,7 +1042,7 @@
         <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1032,7 +1050,7 @@
         <v>85</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1040,7 +1058,7 @@
         <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1048,7 +1066,7 @@
         <v>74</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1056,7 +1074,7 @@
         <v>75</v>
       </c>
       <c r="B38" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1064,7 +1082,7 @@
         <v>83</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1072,7 +1090,7 @@
         <v>76</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1080,7 +1098,7 @@
         <v>77</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1088,7 +1106,7 @@
         <v>78</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1096,7 +1114,7 @@
         <v>79</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1104,7 +1122,7 @@
         <v>80</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1112,7 +1130,7 @@
         <v>81</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1120,7 +1138,7 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1128,7 +1146,7 @@
         <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1141,7 +1159,7 @@
         <v>87</v>
       </c>
       <c r="B49" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1149,7 +1167,7 @@
         <v>88</v>
       </c>
       <c r="B50" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1157,7 +1175,7 @@
         <v>89</v>
       </c>
       <c r="B51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1165,7 +1183,7 @@
         <v>90</v>
       </c>
       <c r="B52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1173,7 +1191,7 @@
         <v>91</v>
       </c>
       <c r="B53" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1181,7 +1199,7 @@
         <v>21</v>
       </c>
       <c r="B54" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
@@ -1194,7 +1212,7 @@
         <v>23</v>
       </c>
       <c r="B56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1202,7 +1220,7 @@
         <v>68</v>
       </c>
       <c r="B57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1210,7 +1228,7 @@
         <v>24</v>
       </c>
       <c r="B58" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1218,7 +1236,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1226,7 +1244,7 @@
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1234,7 +1252,7 @@
         <v>27</v>
       </c>
       <c r="B61" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
@@ -1247,7 +1265,7 @@
         <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1255,251 +1273,263 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B65" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>31</v>
       </c>
       <c r="B66" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="C66" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>34</v>
       </c>
       <c r="B68" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="C68" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B69" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B71" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B72" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B73" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B74" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="C74" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B76" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B77" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>44</v>
       </c>
       <c r="B78" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="s">
         <v>95</v>
       </c>
       <c r="B80" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="s">
         <v>94</v>
       </c>
       <c r="B81" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="s">
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="6" t="s">
         <v>46</v>
       </c>
       <c r="B83" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B84" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+      <c r="C84" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
         <v>47</v>
       </c>
       <c r="B85" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="s">
         <v>48</v>
       </c>
       <c r="B89" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B91" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B92" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B94" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="3" t="s">
         <v>54</v>
       </c>
       <c r="B95" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>55</v>
       </c>
       <c r="B96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1507,11 +1537,11 @@
         <v>56</v>
       </c>
       <c r="B97" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A97" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:B97" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Команды распознание.xlsx
+++ b/Команды распознание.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Toxa\Desktop\VK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F81F14-510A-4A6F-971B-459A7C24A480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D8AE66-6402-43E0-8F6F-EA2A8AAE98A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="104">
   <si>
     <t>Команды Жабабота</t>
   </si>
@@ -340,6 +340,12 @@
   </si>
   <si>
     <t>+</t>
+  </si>
+  <si>
+    <t>В процессе</t>
+  </si>
+  <si>
+    <t>Доделать распознавание. Надо делать уже после огорода, чтобы добавить выпадающие семена</t>
   </si>
 </sst>
 </file>
@@ -827,7 +833,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -835,7 +841,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
         <v>101</v>
@@ -857,7 +863,7 @@
         <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -984,7 +990,7 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">

--- a/Команды распознание.xlsx
+++ b/Команды распознание.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Toxa\Desktop\VK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D8AE66-6402-43E0-8F6F-EA2A8AAE98A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE7E09F-9411-42F8-B260-F2771D4BB96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Команды Жабабота" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Команды Жабабота'!$A$1:$B$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Команды Жабабота'!$A$1:$B$98</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="105">
   <si>
     <t>Команды Жабабота</t>
   </si>
@@ -342,10 +342,13 @@
     <t>+</t>
   </si>
   <si>
-    <t>В процессе</t>
-  </si>
-  <si>
     <t>Доделать распознавание. Надо делать уже после огорода, чтобы добавить выпадающие семена</t>
+  </si>
+  <si>
+    <t>Открыть стоп-лист</t>
+  </si>
+  <si>
+    <t>ваываы</t>
   </si>
 </sst>
 </file>
@@ -781,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="80" customWidth="1"/>
@@ -833,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -841,7 +844,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
         <v>101</v>
@@ -990,7 +993,7 @@
         <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1271,7 +1274,7 @@
         <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1546,8 +1549,17 @@
         <v>99</v>
       </c>
     </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B98" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B97" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:B98" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>